--- a/xlsx/tests/templates/invoice.xlsx
+++ b/xlsx/tests/templates/invoice.xlsx
@@ -5,16 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dg-ac/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dg-ac/Documents/IronCalc Mkt/Templates/final/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C112375-00AE-334D-AB45-6677B0996D91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{050D83BB-4D47-A74A-8915-EC6995795A05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Invoice" sheetId="1" r:id="rId1"/>
     <sheet name="Settings" sheetId="2" r:id="rId2"/>
+    <sheet name="METADATA" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="AccountHolder">Settings!$C$13</definedName>
@@ -70,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="53">
   <si>
     <t>IronCalc GmbH</t>
   </si>
@@ -226,6 +227,9 @@
   </si>
   <si>
     <t>Invoice Footer Note</t>
+  </si>
+  <si>
+    <t>NOW</t>
   </si>
 </sst>
 </file>
@@ -443,7 +447,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -553,6 +557,7 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Input" xfId="1" builtinId="20"/>
@@ -953,7 +958,7 @@
       </c>
       <c r="H4" s="12">
         <f ca="1">TODAY()</f>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="I4" s="2"/>
     </row>
@@ -971,7 +976,7 @@
       </c>
       <c r="H5" s="12">
         <f ca="1">WORKDAY(H4,PaymentTermsDays)</f>
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="I5" s="2"/>
     </row>
@@ -1734,4 +1739,26 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59EC5DAC-AC0C-1D46-AE7A-BB96D5D604B4}">
+  <dimension ref="A2:B2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" s="37">
+        <f ca="1">NOW()</f>
+        <v>46226.524244328706</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/xlsx/tests/templates/invoice.xlsx
+++ b/xlsx/tests/templates/invoice.xlsx
@@ -5,17 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dg-ac/Documents/IronCalc Mkt/Templates/final/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dg-ac/Documents/IronCalc Mkt/Templates/v0.8.02/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{050D83BB-4D47-A74A-8915-EC6995795A05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{334CE5B4-A02F-DD4D-AC4B-50B1D49596C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Invoice" sheetId="1" r:id="rId1"/>
     <sheet name="Settings" sheetId="2" r:id="rId2"/>
-    <sheet name="METADATA" sheetId="3" r:id="rId3"/>
+    <sheet name="METADATA" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="AccountHolder">Settings!$C$13</definedName>
@@ -958,7 +958,7 @@
       </c>
       <c r="H4" s="12">
         <f ca="1">TODAY()</f>
-        <v>46226</v>
+        <v>46233</v>
       </c>
       <c r="I4" s="2"/>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="H5" s="12">
         <f ca="1">WORKDAY(H4,PaymentTermsDays)</f>
-        <v>46268</v>
+        <v>46275</v>
       </c>
       <c r="I5" s="2"/>
     </row>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="B2" s="37">
         <f ca="1">NOW()</f>
-        <v>46226.524244328706</v>
+        <v>46233.61136145833</v>
       </c>
     </row>
   </sheetData>
